--- a/Appliccativo_appwitch/Archivio verifiche/Template_VSE.xlsx
+++ b/Appliccativo_appwitch/Archivio verifiche/Template_VSE.xlsx
@@ -3431,6 +3431,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39CABB39-C6EA-4815-9263-A3E875FD4E70}">
   <sheetPr codeName="Foglio1"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:AJ122"/>
   <sheetFormatPr defaultColWidth="5.7109375" defaultRowHeight="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
